--- a/artfynd/A 9028-2025 artfynd.xlsx
+++ b/artfynd/A 9028-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129352630</v>
       </c>
       <c r="B2" t="n">
-        <v>90303</v>
+        <v>90304</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129352629</v>
       </c>
       <c r="B3" t="n">
-        <v>86886</v>
+        <v>86887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129352627</v>
       </c>
       <c r="B4" t="n">
-        <v>87023</v>
+        <v>87024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 9028-2025 artfynd.xlsx
+++ b/artfynd/A 9028-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129352630</v>
       </c>
       <c r="B2" t="n">
-        <v>90304</v>
+        <v>90307</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129352629</v>
       </c>
       <c r="B3" t="n">
-        <v>86887</v>
+        <v>86890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129352627</v>
       </c>
       <c r="B4" t="n">
-        <v>87024</v>
+        <v>87027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 9028-2025 artfynd.xlsx
+++ b/artfynd/A 9028-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129352630</v>
       </c>
       <c r="B2" t="n">
-        <v>90307</v>
+        <v>90309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129352629</v>
       </c>
       <c r="B3" t="n">
-        <v>86890</v>
+        <v>86892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129352627</v>
       </c>
       <c r="B4" t="n">
-        <v>87027</v>
+        <v>87029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,6 +963,200 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129482590</v>
+      </c>
+      <c r="B5" t="n">
+        <v>87023</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Byrum, Öl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>620013</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6345890</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Julien Hach</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Julien Hach</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129482613</v>
+      </c>
+      <c r="B6" t="n">
+        <v>86859</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>439</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sydlig gyllenspindling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cortinarius bergeronii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Melot) Melot</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Byrum, Öl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>620013</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6345890</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Julien Hach</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Julien Hach</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9028-2025 artfynd.xlsx
+++ b/artfynd/A 9028-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129352630</v>
       </c>
       <c r="B2" t="n">
-        <v>90309</v>
+        <v>90313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129352629</v>
       </c>
       <c r="B3" t="n">
-        <v>86892</v>
+        <v>86896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129352627</v>
       </c>
       <c r="B4" t="n">
-        <v>87029</v>
+        <v>87033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129482590</v>
       </c>
       <c r="B5" t="n">
-        <v>87023</v>
+        <v>87027</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,6 +995,9 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Byrum, Öl</t>
@@ -1045,6 +1048,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1056,7 +1060,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Julien Hach</t>
+          <t>Julien Hach, Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1066,7 +1070,7 @@
         <v>129482613</v>
       </c>
       <c r="B6" t="n">
-        <v>86859</v>
+        <v>86863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,6 +1096,9 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Byrum, Öl</t>
@@ -1142,6 +1149,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1153,7 +1161,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Julien Hach</t>
+          <t>Julien Hach, Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 9028-2025 artfynd.xlsx
+++ b/artfynd/A 9028-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129352630</v>
       </c>
       <c r="B2" t="n">
-        <v>90313</v>
+        <v>90314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129352629</v>
       </c>
       <c r="B3" t="n">
-        <v>86896</v>
+        <v>86897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129352627</v>
       </c>
       <c r="B4" t="n">
-        <v>87033</v>
+        <v>87034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129482590</v>
       </c>
       <c r="B5" t="n">
-        <v>87027</v>
+        <v>87028</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>129482613</v>
       </c>
       <c r="B6" t="n">
-        <v>86863</v>
+        <v>86864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9028-2025 artfynd.xlsx
+++ b/artfynd/A 9028-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1166,6 +1166,107 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129482544</v>
+      </c>
+      <c r="B7" t="n">
+        <v>86921</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Byrum, Öl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>620013</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6345890</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Julien Hach</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Julien Hach, Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9028-2025 artfynd.xlsx
+++ b/artfynd/A 9028-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129352630</v>
       </c>
       <c r="B2" t="n">
-        <v>90314</v>
+        <v>90317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9028-2025 artfynd.xlsx
+++ b/artfynd/A 9028-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129352630</v>
       </c>
       <c r="B2" t="n">
-        <v>90317</v>
+        <v>90345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129352629</v>
       </c>
       <c r="B3" t="n">
-        <v>86897</v>
+        <v>86925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129352627</v>
       </c>
       <c r="B4" t="n">
-        <v>87034</v>
+        <v>87062</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129482590</v>
       </c>
       <c r="B5" t="n">
-        <v>87028</v>
+        <v>87056</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>129482613</v>
       </c>
       <c r="B6" t="n">
-        <v>86864</v>
+        <v>86892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>129482544</v>
       </c>
       <c r="B7" t="n">
-        <v>86921</v>
+        <v>86949</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9028-2025 artfynd.xlsx
+++ b/artfynd/A 9028-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129352630</v>
       </c>
       <c r="B2" t="n">
-        <v>90345</v>
+        <v>90351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129352629</v>
       </c>
       <c r="B3" t="n">
-        <v>86925</v>
+        <v>86931</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129352627</v>
       </c>
       <c r="B4" t="n">
-        <v>87062</v>
+        <v>87068</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129482590</v>
       </c>
       <c r="B5" t="n">
-        <v>87056</v>
+        <v>87062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>129482613</v>
       </c>
       <c r="B6" t="n">
-        <v>86892</v>
+        <v>86898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>129482544</v>
       </c>
       <c r="B7" t="n">
-        <v>86949</v>
+        <v>86955</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9028-2025 artfynd.xlsx
+++ b/artfynd/A 9028-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129352630</v>
       </c>
       <c r="B2" t="n">
-        <v>90351</v>
+        <v>90352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129352629</v>
       </c>
       <c r="B3" t="n">
-        <v>86931</v>
+        <v>86932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129352627</v>
       </c>
       <c r="B4" t="n">
-        <v>87068</v>
+        <v>87069</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129482590</v>
       </c>
       <c r="B5" t="n">
-        <v>87062</v>
+        <v>87063</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>129482613</v>
       </c>
       <c r="B6" t="n">
-        <v>86898</v>
+        <v>86899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>129482544</v>
       </c>
       <c r="B7" t="n">
-        <v>86955</v>
+        <v>86956</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9028-2025 artfynd.xlsx
+++ b/artfynd/A 9028-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129352630</v>
       </c>
       <c r="B2" t="n">
-        <v>90352</v>
+        <v>90357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129352629</v>
       </c>
       <c r="B3" t="n">
-        <v>86932</v>
+        <v>86937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129352627</v>
       </c>
       <c r="B4" t="n">
-        <v>87069</v>
+        <v>87074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129482590</v>
       </c>
       <c r="B5" t="n">
-        <v>87063</v>
+        <v>87068</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>129482613</v>
       </c>
       <c r="B6" t="n">
-        <v>86899</v>
+        <v>86904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>129482544</v>
       </c>
       <c r="B7" t="n">
-        <v>86956</v>
+        <v>86961</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9028-2025 artfynd.xlsx
+++ b/artfynd/A 9028-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>129482590</v>
       </c>
       <c r="B5" t="n">
-        <v>87068</v>
+        <v>87072</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>129482613</v>
       </c>
       <c r="B6" t="n">
-        <v>86904</v>
+        <v>86908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>129482544</v>
       </c>
       <c r="B7" t="n">
-        <v>86961</v>
+        <v>86965</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9028-2025 artfynd.xlsx
+++ b/artfynd/A 9028-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>129482590</v>
       </c>
       <c r="B5" t="n">
-        <v>87072</v>
+        <v>87074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>129482613</v>
       </c>
       <c r="B6" t="n">
-        <v>86908</v>
+        <v>86910</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>129482544</v>
       </c>
       <c r="B7" t="n">
-        <v>86965</v>
+        <v>86967</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9028-2025 artfynd.xlsx
+++ b/artfynd/A 9028-2025 artfynd.xlsx
@@ -1171,7 +1171,7 @@
         <v>129482544</v>
       </c>
       <c r="B7" t="n">
-        <v>86967</v>
+        <v>86970</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 9028-2025 artfynd.xlsx
+++ b/artfynd/A 9028-2025 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
@@ -1147,7 +1147,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">

--- a/artfynd/A 9028-2025 artfynd.xlsx
+++ b/artfynd/A 9028-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129352630</v>
+        <v>129482613</v>
       </c>
       <c r="B2" t="n">
-        <v>90357</v>
+        <v>87205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1595</v>
+        <v>439</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Sydlig gyllenspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Cortinarius bergeronii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>(Melot) Melot</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Byrum, Byrum, Öl</t>
+          <t>Byrum, Öl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620050</v>
+        <v>620013</v>
       </c>
       <c r="R2" t="n">
-        <v>6345915</v>
+        <v>6345890</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -740,20 +743,21 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -765,17 +769,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Julien Hach, Karin Hjelmér</t>
+          <t>Julien Hach, Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129352629</v>
+        <v>113319943</v>
       </c>
       <c r="B3" t="n">
-        <v>86937</v>
+        <v>87238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,19 +805,20 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Byrum, Byrum, Öl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620050</v>
+        <v>619972</v>
       </c>
       <c r="R3" t="n">
-        <v>6345915</v>
+        <v>6345881</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -862,39 +867,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Julien Hach, Karin Hjelmér</t>
+          <t>Julien Hach</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129352627</v>
+        <v>129352629</v>
       </c>
       <c r="B4" t="n">
-        <v>87074</v>
+        <v>87238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3739</v>
+        <v>445</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620013</v>
+        <v>620050</v>
       </c>
       <c r="R4" t="n">
-        <v>6345890</v>
+        <v>6345915</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,48 +971,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129482590</v>
+        <v>129352630</v>
       </c>
       <c r="B5" t="n">
-        <v>87074</v>
+        <v>90663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>248947</v>
+        <v>1595</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Byrum, Öl</t>
+          <t>Byrum, Byrum, Öl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620013</v>
+        <v>620050</v>
       </c>
       <c r="R5" t="n">
-        <v>6345890</v>
+        <v>6345915</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1034,21 +1036,20 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1060,48 +1061,45 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Julien Hach, Majken Ekstrand</t>
+          <t>Julien Hach, Karin Hjelmér</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129482613</v>
+        <v>129352627</v>
       </c>
       <c r="B6" t="n">
-        <v>86910</v>
+        <v>87375</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>439</v>
+        <v>3739</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydlig gyllenspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius bergeronii</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Melot) Melot</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Byrum, Öl</t>
+          <t>Byrum, Byrum, Öl</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1135,21 +1133,20 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1161,55 +1158,52 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Julien Hach, Majken Ekstrand</t>
+          <t>Julien Hach, Karin Hjelmér</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129482544</v>
+        <v>129352641</v>
       </c>
       <c r="B7" t="n">
-        <v>86970</v>
+        <v>89085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>248956</v>
+        <v>4379</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Byrum, Öl</t>
+          <t>Byrum, Byrum, Öl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620013</v>
+        <v>620098</v>
       </c>
       <c r="R7" t="n">
-        <v>6345890</v>
+        <v>6345931</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1236,12 +1230,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1250,7 +1244,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1262,10 +1255,327 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
+          <t>Julien Hach, Karin Hjelmér</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>101808425</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5333</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>101422</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Hasselbock</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Oberea linearis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1761)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norr Byrum, Öl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>619776</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6345792</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Elfwing</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Elfwing, Carl Tamario, Tobias Berger, Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129482590</v>
+      </c>
+      <c r="B9" t="n">
+        <v>87369</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Byrum, Öl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>620013</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6345890</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Julien Hach</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
           <t>Julien Hach, Majken Ekstrand</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129482544</v>
+      </c>
+      <c r="B10" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Byrum, Öl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>620013</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6345890</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Julien Hach</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Julien Hach, Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
